--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMAdverseDrugReaction.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMAdverseDrugReaction.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:53:12+00:00</t>
+    <t>2026-08-20T15:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -457,7 +457,7 @@
     <t>Type d'effet indésirable provenant du jdv-origine-effet-indesirable-cisis</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-origine-effet-indesirable-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-origine-effet-indesirable-cisis|20260716085851</t>
   </si>
   <si>
     <t>FRLMAdverseDrugReaction.detected</t>
@@ -501,7 +501,7 @@
     <t>Niveau d'imputabilité provenant du jdv-imputabilite-cisis</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-imputabilite-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-imputabilite-cisis|20260716085851</t>
   </si>
   <si>
     <t>FRLMAdverseDrugReaction.severity</t>
@@ -513,7 +513,7 @@
     <t>Gravité provenant du jdv-gravite-cisis</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-gravite-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-gravite-cisis|20260716085852</t>
   </si>
   <si>
     <t>FRLMAdverseDrugReaction.outcome</t>
@@ -525,7 +525,7 @@
     <t>Évolution de l'effet indésirable provenant du jdv-evolution-cisis</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-evolution-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-evolution-cisis|20260716085852</t>
   </si>
 </sst>
 </file>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMAdverseDrugReaction.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMAdverseDrugReaction.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T15:08:45+00:00</t>
+    <t>2026-08-20T15:24:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMAdverseDrugReaction.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMAdverseDrugReaction.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T15:24:46+00:00</t>
+    <t>2026-08-21T08:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMAdverseDrugReaction.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMAdverseDrugReaction.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T08:13:05+00:00</t>
+    <t>2026-08-23T21:45:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMAdverseDrugReaction.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMAdverseDrugReaction.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-23T21:45:18+00:00</t>
+    <t>2026-08-24T13:13:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMAdverseDrugReaction.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMAdverseDrugReaction.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T13:13:01+00:00</t>
+    <t>2026-08-25T11:34:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMAdverseDrugReaction.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMAdverseDrugReaction.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T11:34:21+00:00</t>
+    <t>2026-08-25T11:56:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMAdverseDrugReaction.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMAdverseDrugReaction.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T11:56:50+00:00</t>
+    <t>2026-08-25T20:08:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMAdverseDrugReaction.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMAdverseDrugReaction.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T20:08:46+00:00</t>
+    <t>2026-08-31T08:09:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
